--- a/Hardware/STM32CubeMX/Peripheral Assignment.xlsx
+++ b/Hardware/STM32CubeMX/Peripheral Assignment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joshua/ARGUS/Hardware/STM32CubeMX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8182B3-4BC5-D24E-A687-AD9598D1FDF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73EBA33-C0CF-154B-A825-96729D020D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-8660" windowWidth="51200" windowHeight="28280" xr2:uid="{3DB2BA4E-9560-D249-B14F-B42A0033B67D}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{3DB2BA4E-9560-D249-B14F-B42A0033B67D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="91">
   <si>
     <t>Description</t>
   </si>
@@ -239,9 +239,6 @@
     <t>PD4</t>
   </si>
   <si>
-    <t>UART4</t>
-  </si>
-  <si>
     <t>UART7</t>
   </si>
   <si>
@@ -257,9 +254,6 @@
     <t>To be changed during layout</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>PC14</t>
   </si>
   <si>
@@ -267,6 +261,57 @@
   </si>
   <si>
     <t>PC15</t>
+  </si>
+  <si>
+    <t>DISP</t>
+  </si>
+  <si>
+    <t>Using I2C IO/ADC</t>
+  </si>
+  <si>
+    <t>TIM12_CH1 (PH6)</t>
+  </si>
+  <si>
+    <t>TIM5_CH3 (PH12)</t>
+  </si>
+  <si>
+    <t>TIM12_CH2 (PH9)</t>
+  </si>
+  <si>
+    <t>TIM5_CH2 (PH11)</t>
+  </si>
+  <si>
+    <t>PG2</t>
+  </si>
+  <si>
+    <t>Encoders</t>
+  </si>
+  <si>
+    <t>UART5</t>
+  </si>
+  <si>
+    <t>Encoder 1 A/B</t>
+  </si>
+  <si>
+    <t>Encoder 1 BTN</t>
+  </si>
+  <si>
+    <t>Encoder 2 A/B</t>
+  </si>
+  <si>
+    <t>Encoder 2 BTN</t>
+  </si>
+  <si>
+    <t>TIM2_CH1/CH2</t>
+  </si>
+  <si>
+    <t>TIM3_CH1/CH2</t>
+  </si>
+  <si>
+    <t>EXTI0</t>
+  </si>
+  <si>
+    <t>EXTI2</t>
   </si>
 </sst>
 </file>
@@ -296,12 +341,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -316,7 +367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -324,6 +375,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E69C016D-99C6-D945-BADD-A95B502002E4}">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
@@ -722,373 +774,391 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
         <v>22</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
         <v>24</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+      <c r="C25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" t="s">
-        <v>69</v>
+        <v>28</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
         <v>34</v>
       </c>
-      <c r="C35" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+      <c r="C36" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
         <v>37</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
+    <row r="43" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
         <v>40</v>
       </c>
-      <c r="C42" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
-        <v>39</v>
-      </c>
-      <c r="C43" t="s">
-        <v>72</v>
-      </c>
-      <c r="D43" s="4"/>
+      <c r="C43" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
         <v>41</v>
       </c>
-      <c r="C44" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44" s="4"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B45" s="2" t="s">
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B46" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C45" t="s">
-        <v>72</v>
-      </c>
-      <c r="D45" s="4"/>
-    </row>
-    <row r="46" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+    </row>
+    <row r="47" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
         <v>43</v>
       </c>
-      <c r="C46" t="s">
-        <v>72</v>
-      </c>
-      <c r="D46" s="4"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
-        <v>44</v>
-      </c>
-      <c r="C47" t="s">
-        <v>72</v>
-      </c>
+      <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>45</v>
-      </c>
-      <c r="C48" t="s">
-        <v>72</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C48" s="4"/>
       <c r="D48" s="4"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" t="s">
-        <v>72</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C49" s="4"/>
       <c r="D49" s="4"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>47</v>
-      </c>
-      <c r="C50" t="s">
-        <v>72</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C50" s="4"/>
       <c r="D50" s="4"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>48</v>
-      </c>
-      <c r="C51" t="s">
-        <v>72</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C51" s="4"/>
       <c r="D51" s="4"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" t="s">
-        <v>72</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C52" s="4"/>
       <c r="D52" s="4"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>50</v>
-      </c>
-      <c r="C53" t="s">
-        <v>72</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C53" s="4"/>
       <c r="D53" s="4"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>51</v>
-      </c>
-      <c r="C54" t="s">
-        <v>72</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="C54" s="4"/>
       <c r="D54" s="4"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>52</v>
-      </c>
-      <c r="C55" t="s">
-        <v>72</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C55" s="4"/>
       <c r="D55" s="4"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
         <v>53</v>
       </c>
-      <c r="C56" t="s">
-        <v>72</v>
-      </c>
-      <c r="D56" s="4"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C57" s="4"/>
       <c r="D57" s="4"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="1" t="s">
+      <c r="D58" s="4"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="D58" s="4"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B59" t="s">
-        <v>55</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D59" s="4"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D60" s="4"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D61" s="4"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
+        <v>57</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D62" s="4"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B63" t="s">
         <v>58</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D62" s="4"/>
+      <c r="C63" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D63" s="4"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>83</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
+        <v>84</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B68" t="s">
+        <v>85</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>86</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D42:D62"/>
+  <mergeCells count="2">
+    <mergeCell ref="D43:D63"/>
+    <mergeCell ref="C43:C57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
